--- a/Team-Data/2012-13/4-3-2012-13.xlsx
+++ b/Team-Data/2012-13/4-3-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,25 +728,25 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E2" t="n">
         <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>0.553</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J2" t="n">
-        <v>80.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>0.465</v>
@@ -694,25 +761,25 @@
         <v>0.377</v>
       </c>
       <c r="O2" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="P2" t="n">
         <v>19.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.709</v>
+        <v>0.712</v>
       </c>
       <c r="R2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U2" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="V2" t="n">
         <v>15</v>
@@ -721,43 +788,43 @@
         <v>8.1</v>
       </c>
       <c r="X2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y2" t="n">
         <v>4.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AA2" t="n">
         <v>18.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
       </c>
       <c r="AE2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF2" t="n">
         <v>11</v>
       </c>
-      <c r="AF2" t="n">
-        <v>13</v>
-      </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>11</v>
       </c>
       <c r="AI2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
         <v>6</v>
@@ -778,7 +845,7 @@
         <v>27</v>
       </c>
       <c r="AQ2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR2" t="n">
         <v>27</v>
@@ -796,16 +863,16 @@
         <v>22</v>
       </c>
       <c r="AW2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
         <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
         <v>26</v>
@@ -814,7 +881,7 @@
         <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3" t="n">
         <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>0.52</v>
+        <v>0.514</v>
       </c>
       <c r="H3" t="n">
         <v>49.1</v>
@@ -861,10 +928,10 @@
         <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L3" t="n">
         <v>6.1</v>
@@ -882,10 +949,10 @@
         <v>21.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="S3" t="n">
         <v>31.4</v>
@@ -894,10 +961,10 @@
         <v>39.5</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V3" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W3" t="n">
         <v>8.300000000000001</v>
@@ -906,10 +973,10 @@
         <v>4.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA3" t="n">
         <v>19.6</v>
@@ -918,25 +985,25 @@
         <v>96.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -954,16 +1021,16 @@
         <v>17</v>
       </c>
       <c r="AO3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ3" t="n">
         <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS3" t="n">
         <v>11</v>
@@ -972,13 +1039,13 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV3" t="n">
         <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX3" t="n">
         <v>22</v>
@@ -987,16 +1054,16 @@
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA3" t="n">
         <v>17</v>
       </c>
       <c r="BB3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F4" t="n">
         <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>0.581</v>
+        <v>0.575</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J4" t="n">
         <v>79.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.448</v>
+        <v>0.446</v>
       </c>
       <c r="L4" t="n">
         <v>7.7</v>
@@ -1055,7 +1122,7 @@
         <v>21.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.358</v>
+        <v>0.356</v>
       </c>
       <c r="O4" t="n">
         <v>17.4</v>
@@ -1067,16 +1134,16 @@
         <v>0.733</v>
       </c>
       <c r="R4" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S4" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T4" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U4" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V4" t="n">
         <v>14.8</v>
@@ -1094,16 +1161,16 @@
         <v>18.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.40000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1124,7 +1191,7 @@
         <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1133,10 +1200,10 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AO4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP4" t="n">
         <v>7</v>
@@ -1145,10 +1212,10 @@
         <v>24</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1157,16 +1224,16 @@
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
         <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
         <v>4</v>
@@ -1175,7 +1242,7 @@
         <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
         <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1234,64 +1301,64 @@
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O5" t="n">
         <v>19.1</v>
       </c>
       <c r="P5" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.747</v>
+        <v>0.746</v>
       </c>
       <c r="R5" t="n">
         <v>11.2</v>
       </c>
       <c r="S5" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T5" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="U5" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="V5" t="n">
         <v>13.9</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X5" t="n">
         <v>5.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA5" t="n">
         <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG5" t="n">
         <v>30</v>
@@ -1318,7 +1385,7 @@
         <v>27</v>
       </c>
       <c r="AO5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP5" t="n">
         <v>4</v>
@@ -1333,10 +1400,10 @@
         <v>29</v>
       </c>
       <c r="AT5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AV5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1485,7 +1552,7 @@
         <v>26</v>
       </c>
       <c r="AJ6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
@@ -1509,7 +1576,7 @@
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>14</v>
@@ -1521,13 +1588,13 @@
         <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
@@ -1539,7 +1606,7 @@
         <v>18</v>
       </c>
       <c r="BB6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -1571,46 +1638,46 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E7" t="n">
         <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7" t="n">
-        <v>0.297</v>
+        <v>0.301</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J7" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L7" t="n">
         <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O7" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P7" t="n">
         <v>22.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.755</v>
+        <v>0.753</v>
       </c>
       <c r="R7" t="n">
         <v>12.1</v>
@@ -1619,13 +1686,13 @@
         <v>28.4</v>
       </c>
       <c r="T7" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U7" t="n">
         <v>20.7</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W7" t="n">
         <v>8.1</v>
@@ -1634,7 +1701,7 @@
         <v>3.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Z7" t="n">
         <v>21.2</v>
@@ -1643,13 +1710,13 @@
         <v>19.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.8</v>
+        <v>-4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1691,7 +1758,7 @@
         <v>17</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
@@ -1703,7 +1770,7 @@
         <v>25</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>14</v>
@@ -1715,7 +1782,7 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA7" t="n">
         <v>15</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>-1.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1849,7 +1916,7 @@
         <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK8" t="n">
         <v>9</v>
@@ -1864,10 +1931,10 @@
         <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1882,7 +1949,7 @@
         <v>16</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
         <v>8</v>
@@ -1900,7 +1967,7 @@
         <v>23</v>
       </c>
       <c r="BA8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
         <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1953,10 +2020,10 @@
         <v>40.5</v>
       </c>
       <c r="J9" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L9" t="n">
         <v>6.3</v>
@@ -1965,25 +2032,25 @@
         <v>18.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O9" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P9" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7</v>
+        <v>0.699</v>
       </c>
       <c r="R9" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="S9" t="n">
         <v>31.4</v>
       </c>
       <c r="T9" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U9" t="n">
         <v>24.2</v>
@@ -1992,7 +2059,7 @@
         <v>15.2</v>
       </c>
       <c r="W9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X9" t="n">
         <v>6.5</v>
@@ -2001,19 +2068,19 @@
         <v>6.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA9" t="n">
         <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>105.7</v>
+        <v>105.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2025,7 +2092,7 @@
         <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2043,7 +2110,7 @@
         <v>19</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
         <v>6</v>
@@ -2058,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT9" t="n">
         <v>4</v>
@@ -2073,13 +2140,13 @@
         <v>2</v>
       </c>
       <c r="AX9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -2117,70 +2184,70 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" t="n">
         <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>0.329</v>
+        <v>0.333</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J10" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K10" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L10" t="n">
         <v>6.2</v>
       </c>
       <c r="M10" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.354</v>
+        <v>0.357</v>
       </c>
       <c r="O10" t="n">
         <v>15.7</v>
       </c>
       <c r="P10" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q10" t="n">
         <v>0.697</v>
       </c>
       <c r="R10" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T10" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="U10" t="n">
         <v>21.1</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W10" t="n">
         <v>6.8</v>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z10" t="n">
         <v>19.6</v>
@@ -2213,19 +2280,19 @@
         <v>24</v>
       </c>
       <c r="AJ10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
         <v>23</v>
       </c>
       <c r="AM10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>23</v>
@@ -2237,22 +2304,22 @@
         <v>29</v>
       </c>
       <c r="AR10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU10" t="n">
         <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX10" t="n">
         <v>16</v>
@@ -2261,7 +2328,7 @@
         <v>21</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>0.573</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2323,22 +2390,22 @@
         <v>0.456</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
         <v>19.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.399</v>
+        <v>0.4</v>
       </c>
       <c r="O11" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P11" t="n">
         <v>21.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R11" t="n">
         <v>10.8</v>
@@ -2350,16 +2417,16 @@
         <v>44.9</v>
       </c>
       <c r="U11" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V11" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W11" t="n">
         <v>6.8</v>
       </c>
       <c r="X11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y11" t="n">
         <v>4.9</v>
@@ -2368,16 +2435,16 @@
         <v>21.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2434,25 +2501,25 @@
         <v>25</v>
       </c>
       <c r="AW11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX11" t="n">
         <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -2481,22 +2548,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
         <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J12" t="n">
         <v>82.7</v>
@@ -2511,16 +2578,16 @@
         <v>28.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O12" t="n">
         <v>19.1</v>
       </c>
       <c r="P12" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R12" t="n">
         <v>11.1</v>
@@ -2529,10 +2596,10 @@
         <v>32.1</v>
       </c>
       <c r="T12" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U12" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V12" t="n">
         <v>16.4</v>
@@ -2547,28 +2614,28 @@
         <v>6.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA12" t="n">
         <v>20.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>106</v>
+        <v>105.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF12" t="n">
         <v>11</v>
       </c>
       <c r="AG12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
@@ -2625,7 +2692,7 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>5.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2753,31 +2820,31 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
         <v>26</v>
       </c>
       <c r="AL13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM13" t="n">
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
         <v>18</v>
@@ -2801,13 +2868,13 @@
         <v>23</v>
       </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY13" t="n">
         <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
         <v>3</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -2845,28 +2912,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
         <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>0.658</v>
+        <v>0.653</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J14" t="n">
-        <v>80.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L14" t="n">
         <v>7.6</v>
@@ -2875,13 +2942,13 @@
         <v>21.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O14" t="n">
         <v>16.6</v>
       </c>
       <c r="P14" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0.71</v>
@@ -2893,19 +2960,19 @@
         <v>29.9</v>
       </c>
       <c r="T14" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="V14" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W14" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y14" t="n">
         <v>4.2</v>
@@ -2914,13 +2981,13 @@
         <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>101</v>
+        <v>100.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2935,10 +3002,10 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ14" t="n">
         <v>25</v>
@@ -2953,22 +3020,22 @@
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR14" t="n">
         <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT14" t="n">
         <v>20</v>
@@ -2977,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2989,13 +3056,13 @@
         <v>5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
       </c>
       <c r="BB14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>14</v>
@@ -3138,7 +3205,7 @@
         <v>16</v>
       </c>
       <c r="AO15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
@@ -3165,13 +3232,13 @@
         <v>23</v>
       </c>
       <c r="AX15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
         <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
         <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,7 +3294,7 @@
         <v>36.3</v>
       </c>
       <c r="J16" t="n">
-        <v>81.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0.445</v>
@@ -3242,10 +3309,10 @@
         <v>0.348</v>
       </c>
       <c r="O16" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P16" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q16" t="n">
         <v>0.778</v>
@@ -3254,16 +3321,16 @@
         <v>13</v>
       </c>
       <c r="S16" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T16" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U16" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V16" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W16" t="n">
         <v>8.6</v>
@@ -3272,7 +3339,7 @@
         <v>5.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z16" t="n">
         <v>20.2</v>
@@ -3284,10 +3351,10 @@
         <v>93.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3305,10 +3372,10 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3320,10 +3387,10 @@
         <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
         <v>6</v>
@@ -3347,7 +3414,7 @@
         <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
@@ -3356,13 +3423,13 @@
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB16" t="n">
         <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3502,7 +3569,7 @@
         <v>2</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
         <v>3</v>
@@ -3529,7 +3596,7 @@
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -3573,25 +3640,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" t="n">
         <v>36</v>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>0.486</v>
+        <v>0.493</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J18" t="n">
-        <v>87.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="K18" t="n">
         <v>0.437</v>
@@ -3606,16 +3673,16 @@
         <v>0.359</v>
       </c>
       <c r="O18" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="n">
         <v>0.741</v>
       </c>
       <c r="R18" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S18" t="n">
         <v>30.8</v>
@@ -3624,16 +3691,16 @@
         <v>43.9</v>
       </c>
       <c r="U18" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V18" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W18" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="Y18" t="n">
         <v>4.5</v>
@@ -3645,13 +3712,13 @@
         <v>19.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.2</v>
+        <v>99.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
@@ -3663,10 +3730,10 @@
         <v>17</v>
       </c>
       <c r="AH18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3675,16 +3742,16 @@
         <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM18" t="n">
         <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP18" t="n">
         <v>23</v>
@@ -3702,10 +3769,10 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW18" t="n">
         <v>10</v>
@@ -3714,13 +3781,13 @@
         <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F19" t="n">
         <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>0.378</v>
+        <v>0.37</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J19" t="n">
         <v>81.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L19" t="n">
         <v>5.4</v>
@@ -3785,13 +3852,13 @@
         <v>17.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.303</v>
+        <v>0.3</v>
       </c>
       <c r="O19" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P19" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q19" t="n">
         <v>0.735</v>
@@ -3806,43 +3873,43 @@
         <v>42.4</v>
       </c>
       <c r="U19" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V19" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W19" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X19" t="n">
         <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z19" t="n">
         <v>18.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.59999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF19" t="n">
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
@@ -3872,34 +3939,34 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU19" t="n">
         <v>16</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX19" t="n">
         <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
@@ -3908,7 +3975,7 @@
         <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -3937,22 +4004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E20" t="n">
         <v>26</v>
       </c>
       <c r="F20" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G20" t="n">
-        <v>0.347</v>
+        <v>0.351</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J20" t="n">
         <v>80.2</v>
@@ -3967,7 +4034,7 @@
         <v>18.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O20" t="n">
         <v>15</v>
@@ -4003,19 +4070,19 @@
         <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>94.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
         <v>25</v>
@@ -4039,7 +4106,7 @@
         <v>13</v>
       </c>
       <c r="AL20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM20" t="n">
         <v>21</v>
@@ -4054,7 +4121,7 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>12</v>
@@ -4063,16 +4130,16 @@
         <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU20" t="n">
         <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX20" t="n">
         <v>8</v>
@@ -4090,7 +4157,7 @@
         <v>24</v>
       </c>
       <c r="BC20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E21" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F21" t="n">
         <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.649</v>
+        <v>0.644</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4140,22 +4207,22 @@
         <v>81</v>
       </c>
       <c r="K21" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L21" t="n">
         <v>10.7</v>
       </c>
       <c r="M21" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="N21" t="n">
         <v>0.374</v>
       </c>
       <c r="O21" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="P21" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q21" t="n">
         <v>0.759</v>
@@ -4167,7 +4234,7 @@
         <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U21" t="n">
         <v>19.2</v>
@@ -4176,10 +4243,10 @@
         <v>12.2</v>
       </c>
       <c r="W21" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
         <v>3.9</v>
@@ -4188,19 +4255,19 @@
         <v>20.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF21" t="n">
         <v>6</v>
@@ -4215,10 +4282,10 @@
         <v>23</v>
       </c>
       <c r="AJ21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4230,7 +4297,7 @@
         <v>6</v>
       </c>
       <c r="AO21" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AP21" t="n">
         <v>16</v>
@@ -4239,7 +4306,7 @@
         <v>14</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>25</v>
@@ -4248,7 +4315,7 @@
         <v>26</v>
       </c>
       <c r="AU21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4272,7 +4339,7 @@
         <v>11</v>
       </c>
       <c r="BC21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4448,7 +4515,7 @@
         <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G23" t="n">
-        <v>0.25</v>
+        <v>0.253</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J23" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K23" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L23" t="n">
         <v>6.4</v>
       </c>
       <c r="M23" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N23" t="n">
         <v>0.331</v>
@@ -4519,19 +4586,19 @@
         <v>12.5</v>
       </c>
       <c r="P23" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R23" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U23" t="n">
         <v>22.9</v>
@@ -4552,13 +4619,13 @@
         <v>19.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4609,16 +4676,16 @@
         <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV23" t="n">
         <v>11</v>
       </c>
       <c r="AW23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX23" t="n">
         <v>25</v>
@@ -4627,7 +4694,7 @@
         <v>18</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -4665,37 +4732,37 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" t="n">
         <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>0.405</v>
+        <v>0.411</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="J24" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.444</v>
+        <v>0.446</v>
       </c>
       <c r="L24" t="n">
         <v>6.2</v>
       </c>
       <c r="M24" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O24" t="n">
         <v>12</v>
@@ -4704,25 +4771,25 @@
         <v>16.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.721</v>
+        <v>0.72</v>
       </c>
       <c r="R24" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S24" t="n">
         <v>30.4</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U24" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V24" t="n">
         <v>13.1</v>
       </c>
       <c r="W24" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X24" t="n">
         <v>4.8</v>
@@ -4737,13 +4804,13 @@
         <v>16.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4764,7 +4831,7 @@
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4785,28 +4852,28 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
       </c>
       <c r="AW24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX24" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ24" t="n">
         <v>7</v>
@@ -4815,10 +4882,10 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G25" t="n">
-        <v>0.307</v>
+        <v>0.311</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
@@ -4865,10 +4932,10 @@
         <v>37.1</v>
       </c>
       <c r="J25" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L25" t="n">
         <v>5.7</v>
@@ -4877,16 +4944,16 @@
         <v>17.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="O25" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="P25" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.739</v>
+        <v>0.735</v>
       </c>
       <c r="R25" t="n">
         <v>11.8</v>
@@ -4901,13 +4968,13 @@
         <v>22.4</v>
       </c>
       <c r="V25" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W25" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y25" t="n">
         <v>5</v>
@@ -4916,16 +4983,16 @@
         <v>20.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.7</v>
+        <v>-6.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
@@ -4952,7 +5019,7 @@
         <v>27</v>
       </c>
       <c r="AM25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN25" t="n">
         <v>29</v>
@@ -4964,13 +5031,13 @@
         <v>26</v>
       </c>
       <c r="AQ25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR25" t="n">
         <v>11</v>
       </c>
       <c r="AS25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
@@ -4982,16 +5049,16 @@
         <v>28</v>
       </c>
       <c r="AW25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E26" t="n">
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G26" t="n">
-        <v>0.44</v>
+        <v>0.446</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5050,64 +5117,64 @@
         <v>81.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L26" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M26" t="n">
         <v>23.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P26" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.774</v>
+        <v>0.776</v>
       </c>
       <c r="R26" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S26" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T26" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
         <v>21.8</v>
       </c>
       <c r="V26" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W26" t="n">
         <v>6.6</v>
       </c>
       <c r="X26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y26" t="n">
         <v>4.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA26" t="n">
         <v>19</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.8</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.4</v>
+        <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5122,10 +5189,10 @@
         <v>9</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK26" t="n">
         <v>14</v>
@@ -5137,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AO26" t="n">
         <v>22</v>
@@ -5146,22 +5213,22 @@
         <v>25</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
         <v>21</v>
       </c>
       <c r="AS26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU26" t="n">
         <v>19</v>
       </c>
       <c r="AV26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW26" t="n">
         <v>28</v>
@@ -5170,10 +5237,10 @@
         <v>23</v>
       </c>
       <c r="AY26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA26" t="n">
         <v>25</v>
@@ -5182,7 +5249,7 @@
         <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -5211,46 +5278,46 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E27" t="n">
         <v>27</v>
       </c>
       <c r="F27" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G27" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J27" t="n">
         <v>83.8</v>
       </c>
       <c r="K27" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L27" t="n">
         <v>7.4</v>
       </c>
       <c r="M27" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.365</v>
+        <v>0.366</v>
       </c>
       <c r="O27" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="P27" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R27" t="n">
         <v>11.5</v>
@@ -5265,7 +5332,7 @@
         <v>20.7</v>
       </c>
       <c r="V27" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W27" t="n">
         <v>8.1</v>
@@ -5280,37 +5347,37 @@
         <v>21</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AB27" t="n">
         <v>100</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4.8</v>
+        <v>-4.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
         <v>12</v>
@@ -5322,7 +5389,7 @@
         <v>10</v>
       </c>
       <c r="AO27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AP27" t="n">
         <v>12</v>
@@ -5355,10 +5422,10 @@
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E28" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F28" t="n">
         <v>19</v>
       </c>
       <c r="G28" t="n">
-        <v>0.747</v>
+        <v>0.743</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
@@ -5411,7 +5478,7 @@
         <v>39.4</v>
       </c>
       <c r="J28" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K28" t="n">
         <v>0.486</v>
@@ -5420,28 +5487,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O28" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P28" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.79</v>
+        <v>0.791</v>
       </c>
       <c r="R28" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="S28" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="T28" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U28" t="n">
         <v>25.1</v>
@@ -5453,25 +5520,25 @@
         <v>8.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="AA28" t="n">
         <v>19.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.7</v>
+        <v>103.8</v>
       </c>
       <c r="AC28" t="n">
         <v>7.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5483,13 +5550,13 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5507,13 +5574,13 @@
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
       </c>
       <c r="AR28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS28" t="n">
         <v>5</v>
@@ -5525,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>5</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -5575,58 +5642,58 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F29" t="n">
         <v>47</v>
       </c>
       <c r="G29" t="n">
-        <v>0.373</v>
+        <v>0.365</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
       </c>
       <c r="I29" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J29" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="K29" t="n">
         <v>0.444</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M29" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O29" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P29" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="R29" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S29" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T29" t="n">
         <v>40.1</v>
       </c>
       <c r="U29" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V29" t="n">
         <v>13.7</v>
@@ -5638,31 +5705,31 @@
         <v>4.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z29" t="n">
         <v>22.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB29" t="n">
-        <v>97</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5671,7 +5738,7 @@
         <v>20</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AK29" t="n">
         <v>22</v>
@@ -5683,10 +5750,10 @@
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5695,13 +5762,13 @@
         <v>5</v>
       </c>
       <c r="AR29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU29" t="n">
         <v>20</v>
@@ -5710,13 +5777,13 @@
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX29" t="n">
         <v>20</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5728,7 +5795,7 @@
         <v>16</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E30" t="n">
         <v>39</v>
       </c>
       <c r="F30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.513</v>
+        <v>0.52</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5784,28 +5851,28 @@
         <v>6.1</v>
       </c>
       <c r="M30" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O30" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P30" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R30" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S30" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T30" t="n">
-        <v>42.1</v>
+        <v>42.3</v>
       </c>
       <c r="U30" t="n">
         <v>22.6</v>
@@ -5817,7 +5884,7 @@
         <v>8.4</v>
       </c>
       <c r="X30" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y30" t="n">
         <v>5.9</v>
@@ -5832,7 +5899,7 @@
         <v>98.59999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
@@ -5841,10 +5908,10 @@
         <v>14</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH30" t="n">
         <v>7</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
         <v>7</v>
@@ -5880,16 +5947,16 @@
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
         <v>13</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>6</v>
@@ -5898,7 +5965,7 @@
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
@@ -5910,7 +5977,7 @@
         <v>13</v>
       </c>
       <c r="BC30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E31" t="n">
         <v>28</v>
       </c>
       <c r="F31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G31" t="n">
-        <v>0.373</v>
+        <v>0.378</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="J31" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.433</v>
+        <v>0.434</v>
       </c>
       <c r="L31" t="n">
         <v>6.7</v>
@@ -5969,13 +6036,13 @@
         <v>18.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O31" t="n">
         <v>15.6</v>
       </c>
       <c r="P31" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="Q31" t="n">
         <v>0.735</v>
@@ -5990,7 +6057,7 @@
         <v>43.5</v>
       </c>
       <c r="U31" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V31" t="n">
         <v>15.2</v>
@@ -6005,28 +6072,28 @@
         <v>4.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
         <v>19.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>92.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>21</v>
       </c>
       <c r="AF31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH31" t="n">
         <v>9</v>
@@ -6035,7 +6102,7 @@
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK31" t="n">
         <v>29</v>
@@ -6047,19 +6114,19 @@
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP31" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS31" t="n">
         <v>6</v>
@@ -6080,19 +6147,19 @@
         <v>24</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-3-2012-13</t>
+          <t>2013-04-03</t>
         </is>
       </c>
     </row>
